--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104482_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104482_W3.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1784</v>
+        <v>5.271</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4247</v>
+        <v>3.8962</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7538</v>
+        <v>1.3748</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5705</v>
+        <v>2.4963</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1573</v>
+        <v>1.3613</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4132</v>
+        <v>1.1351</v>
       </c>
       <c r="J2" t="n">
-        <v>0.599</v>
+        <v>1.8498</v>
       </c>
       <c r="K2" t="n">
-        <v>0.599</v>
+        <v>1.4479</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.4019</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0285</v>
+        <v>0.6465</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4417</v>
+        <v>-0.0866</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4132</v>
+        <v>0.7331</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3811</v>
+        <v>-0.1359</v>
       </c>
       <c r="T2" t="n">
-        <v>1.733</v>
+        <v>-0.1326</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6481</v>
+        <v>-0.0033</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6311</v>
+        <v>3.5519</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5608</v>
+        <v>2.1872</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0704</v>
+        <v>1.3647</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4947</v>
+        <v>0.5752</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3592</v>
+        <v>0.1579</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1355</v>
+        <v>0.4173</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8624</v>
+        <v>0.5893</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4546</v>
+        <v>0.5893</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4078</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6324</v>
+        <v>-0.0141</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0954</v>
+        <v>-0.4314</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7277</v>
+        <v>0.4173</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7709</v>
+        <v>0.7491</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4869</v>
+        <v>0.5084</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.284</v>
+        <v>0.2407</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1853</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6728</v>
+        <v>2.8555</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2728</v>
+        <v>2.5009</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4</v>
+        <v>0.3545</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7508</v>
+        <v>0.7602</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1848</v>
+        <v>-0.1784</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9356</v>
+        <v>0.9386</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6671</v>
+        <v>1.6625</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3983</v>
+        <v>0.3964</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9162</v>
+        <v>-0.9023</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3049</v>
+        <v>-0.1323</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4869</v>
+        <v>-0.251</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1821</v>
+        <v>0.1187</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9439</v>
+        <v>2.1453</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4482</v>
+        <v>-0.7179</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4957</v>
+        <v>2.8632</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7646</v>
+        <v>-0.468</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0288</v>
+        <v>1.0305</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7933</v>
+        <v>-1.4985</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8825</v>
+        <v>-0.4134</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1692</v>
+        <v>1.017</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7133</v>
+        <v>-1.4303</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1179</v>
+        <v>-0.0546</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.198</v>
+        <v>0.0135</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>2.722</v>
+        <v>3.4145</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2743</v>
+        <v>-0.7039</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3266</v>
+        <v>-0.2072</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0523</v>
+        <v>-0.4967</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7688</v>
+        <v>1.8243</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8114</v>
+        <v>0.6977</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5802</v>
+        <v>1.1266</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4807</v>
+        <v>1.7465</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>-1.031</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5007</v>
+        <v>2.7774</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4018</v>
+        <v>2.8353</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0217</v>
+        <v>0.1477</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4234</v>
+        <v>2.6876</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0789</v>
+        <v>-1.0888</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0017</v>
+        <v>-1.1786</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0772</v>
+        <v>0.0898</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4025</v>
+        <v>2.7316</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.07</v>
+        <v>-0.3774</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3266</v>
+        <v>-0.019</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.3584</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1853</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7255</v>
+        <v>1.6516</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2407</v>
+        <v>-0.3293</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5152</v>
+        <v>1.9809</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2154</v>
+        <v>-1.2543</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3304</v>
+        <v>-0.1295</v>
       </c>
       <c r="I7" t="n">
-        <v>0.885</v>
+        <v>-1.1248</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5343</v>
+        <v>-1.3837</v>
       </c>
       <c r="K7" t="n">
-        <v>2.788</v>
+        <v>0.1584</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7463</v>
+        <v>-1.542</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3189</v>
+        <v>0.1294</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4576</v>
+        <v>-0.2879</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1387</v>
+        <v>0.4173</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1245</v>
+        <v>0.223</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0162</v>
+        <v>-0.0351</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1083</v>
+        <v>0.2581</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>G. PROCIDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2444</v>
+        <v>1.1846</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9026999999999999</v>
+        <v>2.1323</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1471</v>
+        <v>-0.9477</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2565</v>
+        <v>2.1454</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1343</v>
+        <v>0.9243</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1222</v>
+        <v>1.2211</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3693</v>
+        <v>2.7344</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1661</v>
+        <v>1.9305</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5354</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1129</v>
+        <v>-0.589</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3003</v>
+        <v>-1.0062</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1797</v>
+        <v>-0.4844</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6261</v>
+        <v>0.3782</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4464</v>
+        <v>-0.8626</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>-0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. PROCIDA</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.9698</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7332</v>
+        <v>1.3874</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0059</v>
+        <v>-0.4177</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1434</v>
+        <v>3.2204</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9147</v>
+        <v>2.3293</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2287</v>
+        <v>0.8911</v>
       </c>
       <c r="J9" t="n">
-        <v>2.755</v>
+        <v>3.5199</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9395</v>
+        <v>2.7751</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8156</v>
+        <v>0.7447</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6116</v>
+        <v>-0.2995</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0248</v>
+        <v>-0.4458</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4132</v>
+        <v>0.1463</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9379</v>
+        <v>0.3624</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0484</v>
+        <v>0.1925</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8895</v>
+        <v>0.1699</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-1.2472</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3787</v>
+        <v>-0.7561</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1934</v>
+        <v>-1.4384</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1853</v>
+        <v>0.6823</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5194</v>
+        <v>0.4563</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5727</v>
+        <v>-0.5954</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0533</v>
+        <v>1.0516</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8618</v>
+        <v>0.8729</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9737</v>
+        <v>0.3964</v>
       </c>
       <c r="L10" t="n">
-        <v>0.112</v>
+        <v>0.4764</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6576</v>
+        <v>-0.4166</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.599</v>
+        <v>-0.9918</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0586</v>
+        <v>0.5752</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-4.5526</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3014</v>
+        <v>-0.8874</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8026</v>
+        <v>0.0624</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5012</v>
+        <v>-0.9498</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7657</v>
+        <v>-1.653</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2358</v>
+        <v>-1.3896</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4701</v>
+        <v>-0.2634</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4423</v>
+        <v>-1.5241</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6106</v>
+        <v>-1.5793</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0529</v>
+        <v>0.0552</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8807</v>
+        <v>-0.8783</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3983</v>
+        <v>-0.99</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4824</v>
+        <v>0.1117</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4384</v>
+        <v>-0.6458</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0089</v>
+        <v>-0.5893</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5705</v>
+        <v>-0.0565</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5367</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8981</v>
+        <v>0.0289</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7652</v>
+        <v>0.6268</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.133</v>
+        <v>-0.598</v>
       </c>
       <c r="V11" t="n">
-        <v>2.1853</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8201</v>
+        <v>-2.7205</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.519</v>
+        <v>-2.4689</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3011</v>
+        <v>-0.2516</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7846</v>
+        <v>-3.79</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7561</v>
+        <v>-1.7549</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0285</v>
+        <v>-2.0351</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.7489</v>
+        <v>-2.7706</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4644</v>
+        <v>-0.4761</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0357</v>
+        <v>-1.0194</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>0.284</v>
+        <v>0.3867</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2299</v>
+        <v>0.3017</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0541</v>
+        <v>0.0849</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1469</v>
+        <v>-4.1949</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.3619</v>
+        <v>-4.763</v>
       </c>
       <c r="F13" t="n">
-        <v>0.215</v>
+        <v>0.5681</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.7791</v>
+        <v>-3.805</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0258</v>
+        <v>-0.034</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.7532</v>
+        <v>-3.771</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.2124</v>
+        <v>-3.2622</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4636</v>
+        <v>0.4407</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.676</v>
+        <v>-3.7029</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5666</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0465</v>
+        <v>-0.0743</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9739</v>
+        <v>-0.3139</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0726</v>
+        <v>0.2396</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.780800000000003</v>
+        <v>10.1295</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6562</v>
+        <v>1.694600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>8.1248</v>
+        <v>8.434699999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5614000000000012</v>
+        <v>0.5589</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4685</v>
+        <v>0.5007999999999995</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09289999999999976</v>
+        <v>0.05799999999999983</v>
       </c>
       <c r="J14" t="n">
-        <v>5.586799999999998</v>
+        <v>5.3559</v>
       </c>
       <c r="K14" t="n">
-        <v>7.9602</v>
+        <v>7.833299999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.373</v>
+        <v>-2.4774</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.025</v>
+        <v>-4.797</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.4916</v>
+        <v>-7.3325</v>
       </c>
       <c r="O14" t="n">
-        <v>2.4663</v>
+        <v>2.5354</v>
       </c>
       <c r="P14" t="n">
-        <v>4.5368</v>
+        <v>4.552899999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.0125</v>
+        <v>-17.0724</v>
       </c>
       <c r="R14" t="n">
-        <v>21.5492</v>
+        <v>21.6252</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3913</v>
+        <v>-1.0455</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7411000000000001</v>
+        <v>1.1112</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.1324</v>
+        <v>-2.1569</v>
       </c>
       <c r="V14" t="n">
-        <v>6.073899999999999</v>
+        <v>6.063599999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>12.3408</v>
+        <v>12.2998</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.266999999999999</v>
+        <v>-6.2363</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3219</v>
+        <v>3.9888</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2272</v>
+        <v>2.6829</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0947</v>
+        <v>1.3059</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4881</v>
+        <v>0.4974</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2322</v>
+        <v>0.2381</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7375</v>
+        <v>0.7272</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5239</v>
+        <v>1.5168</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2494</v>
+        <v>-0.2298</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1662</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6956</v>
+        <v>-0.2232</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4706</v>
+        <v>-0.2854</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8186</v>
+        <v>2.3246</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2974</v>
+        <v>1.638</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5213</v>
+        <v>0.6865</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0122</v>
+        <v>1.0066</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9135</v>
+        <v>0.9052</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1185</v>
+        <v>1.1064</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1185</v>
+        <v>1.1064</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1063</v>
+        <v>-0.0998</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O16" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0348</v>
+        <v>0.4773</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0181</v>
+        <v>0.3739</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0529</v>
+        <v>0.1035</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5035</v>
+        <v>1.8064</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1671</v>
+        <v>0.2535</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6706</v>
+        <v>1.5528</v>
       </c>
       <c r="G17" t="n">
         <v>3.1011</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6923</v>
       </c>
       <c r="I17" t="n">
-        <v>2.407</v>
+        <v>2.4088</v>
       </c>
       <c r="J17" t="n">
-        <v>3.534</v>
+        <v>3.4988</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5616</v>
+        <v>1.5406</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9724</v>
+        <v>1.9582</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4329</v>
+        <v>-0.3977</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8675</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4346</v>
+        <v>0.4506</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0317</v>
+        <v>0.3474</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2571</v>
+        <v>0.2179</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2888</v>
+        <v>0.1295</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. GARCIA</t>
+          <t>J. JACKSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4434</v>
+        <v>1.2375</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1967</v>
+        <v>2.3063</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2467</v>
+        <v>-1.0688</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0223</v>
+        <v>1.5314</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5425</v>
+        <v>0.7584</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4798</v>
+        <v>0.773</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6837</v>
+        <v>2.316</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0866</v>
+        <v>1.937</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5971</v>
+        <v>0.3789</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3387</v>
+        <v>-0.7846</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4559</v>
+        <v>-1.1786</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1172</v>
+        <v>0.3941</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>3.1868</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3285</v>
+        <v>-0.1637</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6472</v>
+        <v>0.039</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3188</v>
+        <v>-0.2026</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. JACKSON</t>
+          <t>S. GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0131</v>
+        <v>0.0992</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2928</v>
+        <v>-0.2797</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2797</v>
+        <v>0.379</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5376</v>
+        <v>1.0283</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7619</v>
+        <v>0.5455</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7756</v>
+        <v>0.4828</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3596</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9599</v>
+        <v>0.0862</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3997</v>
+        <v>0.5958</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.822</v>
+        <v>0.3463</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.198</v>
+        <v>0.4593</v>
       </c>
       <c r="O19" t="n">
-        <v>0.376</v>
+        <v>-0.113</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0415</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1757</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3807</v>
+        <v>-0.0185</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0253</v>
+        <v>0.1765</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3554</v>
+        <v>-0.195</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3858</v>
+        <v>-0.1975</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0701</v>
+        <v>0.1887</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4559</v>
+        <v>-0.3862</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7421</v>
+        <v>-0.7363</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3103</v>
+        <v>-0.3075</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="J20" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="K20" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.794</v>
+        <v>-0.7881</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0974</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0181</v>
+        <v>0.137</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5078</v>
+        <v>-1.2333</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4584</v>
+        <v>0.8717</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9662</v>
+        <v>-2.105</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8937</v>
+        <v>-0.8824</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5152</v>
+        <v>-0.5087</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3785</v>
+        <v>-0.3737</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1639</v>
+        <v>0.1634</v>
       </c>
       <c r="K21" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L21" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0576</v>
+        <v>-1.0458</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5712</v>
+        <v>0.828</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2945</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2767</v>
+        <v>0.1198</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4061</v>
+        <v>-1.4468</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2491</v>
+        <v>-1.409</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.157</v>
+        <v>-0.0378</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.8876</v>
+        <v>-2.9064</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3922</v>
+        <v>-1.4093</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4954</v>
+        <v>-1.4971</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4541</v>
+        <v>-2.491</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1323</v>
+        <v>-0.1594</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.3218</v>
+        <v>-2.3317</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4335</v>
+        <v>-0.4154</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2671</v>
+        <v>-0.2916</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0484</v>
+        <v>-0.1652</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2187</v>
+        <v>-0.1264</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6544</v>
+        <v>-1.7314</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.078</v>
+        <v>-2.8582</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4236</v>
+        <v>1.1269</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.2109</v>
+        <v>-2.2122</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1082</v>
+        <v>0.1118</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.319</v>
+        <v>-2.324</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6837</v>
+        <v>-1.6967</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6754</v>
+        <v>0.6722</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.3591</v>
+        <v>-2.3689</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5272</v>
+        <v>-0.5155</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O23" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1028</v>
+        <v>0.0256</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2601</v>
+        <v>-0.0234</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3629</v>
+        <v>0.049</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3768</v>
+        <v>-2.2814</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0933</v>
+        <v>-2.2503</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2834</v>
+        <v>-0.0312</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7388</v>
+        <v>0.7328</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7327</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4715</v>
+        <v>1.4842</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2713</v>
+        <v>0.2426</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1967</v>
+        <v>0.1681</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4674</v>
+        <v>0.4901</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O24" t="n">
-        <v>1.3968</v>
+        <v>1.4097</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6372</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2571</v>
+        <v>-0.3743</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3802</v>
+        <v>-0.1634</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4176</v>
+        <v>-4.7284</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3123</v>
+        <v>-3.242</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1053</v>
+        <v>-1.4864</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8256</v>
+        <v>0.8253</v>
       </c>
       <c r="H25" t="n">
-        <v>1.7345</v>
+        <v>1.7293</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9089</v>
+        <v>-0.904</v>
       </c>
       <c r="J25" t="n">
-        <v>2.3041</v>
+        <v>2.2868</v>
       </c>
       <c r="K25" t="n">
-        <v>2.1921</v>
+        <v>2.1751</v>
       </c>
       <c r="L25" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.4785</v>
+        <v>-1.4615</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.8976</v>
+        <v>-5.9184</v>
       </c>
       <c r="Q25" t="n">
-        <v>-6.805</v>
+        <v>-6.8289</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2008</v>
+        <v>0.9094</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8672</v>
+        <v>0.9846</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3336</v>
+        <v>-0.0752</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.1328</v>
+        <v>-7.6186</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.7674</v>
+        <v>-6.3366</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3654</v>
+        <v>-1.282</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.5529</v>
+        <v>-2.5443</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.505</v>
+        <v>-2.5045</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0479</v>
+        <v>-0.0399</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.0614</v>
+        <v>-2.0901</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.7947</v>
+        <v>-1.8141</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.4915</v>
+        <v>-0.4543</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.7103</v>
+        <v>-0.6904</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2187</v>
+        <v>0.2361</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R26" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2604</v>
+        <v>0.2429</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1693</v>
+        <v>0.3061</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0911</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.780799999999999</v>
+        <v>-9.780900000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-8.124600000000001</v>
+        <v>-8.434700000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.655999999999999</v>
+        <v>-1.3463</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5614999999999997</v>
+        <v>-0.5587000000000004</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4685000000000001</v>
+        <v>-0.5009000000000006</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.09310000000000035</v>
+        <v>-0.05809999999999988</v>
       </c>
       <c r="J27" t="n">
-        <v>5.0254</v>
+        <v>4.7971</v>
       </c>
       <c r="K27" t="n">
-        <v>7.491700000000001</v>
+        <v>7.3323</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.4661</v>
+        <v>-2.5354</v>
       </c>
       <c r="M27" t="n">
-        <v>-5.5868</v>
+        <v>-5.3561</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.960100000000001</v>
+        <v>-7.8333</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3731</v>
+        <v>2.4773</v>
       </c>
       <c r="P27" t="n">
-        <v>-4.5365</v>
+        <v>-4.5525</v>
       </c>
       <c r="Q27" t="n">
-        <v>-21.5493</v>
+        <v>-21.625</v>
       </c>
       <c r="R27" t="n">
-        <v>17.0126</v>
+        <v>17.0724</v>
       </c>
       <c r="S27" t="n">
-        <v>1.3912</v>
+        <v>1.394</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1322</v>
+        <v>2.1571</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.7412000000000001</v>
+        <v>-0.7628000000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>-6.0738</v>
+        <v>-6.0634</v>
       </c>
       <c r="W27" t="n">
-        <v>6.2669</v>
+        <v>6.2362</v>
       </c>
       <c r="X27" t="n">
-        <v>-12.3408</v>
+        <v>-12.2997</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104482_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104482_W3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.2363</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104482_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-12.2997</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
